--- a/out/MLP-mamba2_repeat_2_000007.xlsx
+++ b/out/MLP-mamba2_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.818340913531692</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6252523530368312</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.418340913531692</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.818340913531692</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.418340913531692</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002844181210889947</v>
+        <v>-3.858485464146361e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.278920801865005</v>
+        <v>0.444826387838884</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.562910375102412</v>
+        <v>0.8903403969961067</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4916888007696207</v>
+        <v>0.06670370112714537</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.818340913531692</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.262966305951609</v>
+        <v>0.5783243932131673</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6147710428921079</v>
+        <v>0.08340127364901287</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.818340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.00089762920324</v>
+        <v>0.6784339459733786</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8812712118197029</v>
+        <v>0.1195553302535215</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.149016278064389</v>
+        <v>0.8341906120483487</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9427856346348693</v>
+        <v>0.1279008699370345</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.153382412838788</v>
+        <v>0.9704456101738315</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9991627454671981</v>
+        <v>0.1355491425189392</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.208994390261886</v>
+        <v>1.113652703532182</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4509035638265819</v>
+        <v>0.06117014110815683</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.11080832819213</v>
+        <v>1.100332535166175</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2177658120858674</v>
+        <v>0.02954302544213946</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.095082773061586</v>
+        <v>1.098199146423547</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1037595390535334</v>
+        <v>0.01407503353030053</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.084661815490806</v>
+        <v>1.096784679151165</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03074286445690105</v>
+        <v>0.004167188249151734</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.04227820877983</v>
+        <v>1.091030800236881</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02033573889862079</v>
+        <v>0.002754743287663636</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.052190043241371</v>
+        <v>1.092371356319231</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01040622909758016</v>
+        <v>0.001406975593519283</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.05265347118358</v>
+        <v>1.092429907462668</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005320242707164701</v>
+        <v>0.0007177834146964566</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.052882541436309</v>
+        <v>1.092456674214697</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001996960605948998</v>
+        <v>0.000266721685268692</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.051551935424271</v>
+        <v>1.092271786584993</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001086482907913131</v>
+        <v>0.0001426760699292898</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.051726068091265</v>
+        <v>1.092291091180483</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005203164973190552</v>
+        <v>6.652569555024956e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.051680323223337</v>
+        <v>1.092280547595011</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003206891438709984</v>
+        <v>3.927798028457682e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.051800344268736</v>
+        <v>1.092292544413871</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001648459109850995</v>
+        <v>1.764612146467993e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.05181018771423</v>
+        <v>1.09228956294606</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.792472985516974e-05</v>
+        <v>5.990024438636956e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.051800054917489</v>
+        <v>1.092283852383487</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.744500148827117e-05</v>
+        <v>2.674878266576269e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6252523530368312</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.051818263607652</v>
+        <v>1.092282207744528</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.947783683037037e-05</v>
+        <v>-1.503166167089948e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.051808459664555</v>
+        <v>1.092276521466943</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>5.293691574854516e-06</v>
+        <v>-3.970630842514548e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.051800582617643</v>
+        <v>1.092271110997025</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.051796492805153</v>
+        <v>1.092266276362707</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.051790625362468</v>
+        <v>1.092266132378799</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.818340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.051785556007101</v>
+        <v>1.092266109644498</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.051781191033133</v>
+        <v>1.092266427924715</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.051782282279587</v>
+        <v>1.092267519171171</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.051781592672452</v>
+        <v>1.092266829564036</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.051781622984855</v>
+        <v>1.092266859876437</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.051781433532344</v>
+        <v>1.092266670423927</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.051781486579047</v>
+        <v>1.09226672347063</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.051781539625749</v>
+        <v>1.092266776517333</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.051781501735247</v>
+        <v>1.092266738626831</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.051781372907541</v>
+        <v>1.092266609799124</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.051781228923634</v>
+        <v>1.092266465815217</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.051781069783525</v>
+        <v>1.092266306675108</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.05178112283023</v>
+        <v>1.092266359721811</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.051781069783525</v>
+        <v>1.092266306675108</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.051781069783525</v>
+        <v>1.092266306675108</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.051780887909116</v>
+        <v>1.092266124800699</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.051781054627325</v>
+        <v>1.092266291518908</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.051781251657935</v>
+        <v>1.092266488549518</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.051781092517826</v>
+        <v>1.092266329409409</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.418340913531692</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.051781130408328</v>
+        <v>1.092266367299912</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.05178132743894</v>
+        <v>1.092266564330522</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.051781304704638</v>
+        <v>1.09226654159622</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.051781153142629</v>
+        <v>1.092266390034213</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.051781077361627</v>
+        <v>1.092266314253209</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.051781175876931</v>
+        <v>1.092266412768514</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.818340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.051781183455031</v>
+        <v>1.092266420346614</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6252523530368312</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.051781448688544</v>
+        <v>1.092266685580128</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.051781153142629</v>
+        <v>1.092266390034213</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.051781395641843</v>
+        <v>1.092266632533425</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.051781479000946</v>
+        <v>1.09226671589253</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.051781312282737</v>
+        <v>1.092266549174321</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.051781501735247</v>
+        <v>1.092266738626831</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.051781153142629</v>
+        <v>1.092266390034213</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.051780948533919</v>
+        <v>1.092266185425502</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.051781062205425</v>
+        <v>1.092266299097008</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.051781077361627</v>
+        <v>1.092266314253209</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.051780842440515</v>
+        <v>1.092266079332096</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.051780903065316</v>
+        <v>1.0922661399569</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.05178077423761</v>
+        <v>1.092266011129193</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.418340913531692</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.051780910643417</v>
+        <v>1.092266147535</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.051781084939726</v>
+        <v>1.092266321831309</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.051781228923634</v>
+        <v>1.092266465815217</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.225252353036831</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.051781062205425</v>
+        <v>1.092266299097008</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.051781054627325</v>
+        <v>1.092266291518908</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.05178076665951</v>
+        <v>1.092266003551092</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.418340913531692</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.05178078181571</v>
+        <v>1.092266018707293</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.051781009158724</v>
+        <v>1.092266246050305</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.418340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.05178099400252</v>
+        <v>1.092266230894104</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.051781100095928</v>
+        <v>1.09226633698751</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.051780827284311</v>
+        <v>1.092266064175896</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.418340913531692</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.051780925799617</v>
+        <v>1.092266162691201</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6252523530368312</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.051781077361627</v>
+        <v>1.092266314253209</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.051781092517826</v>
+        <v>1.092266329409409</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.051781069783525</v>
+        <v>1.092266306675108</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.818340913531692</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.051781153142629</v>
+        <v>1.092266390034213</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8053588248051395</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.051781251657935</v>
+        <v>1.092266488549518</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.051781084939726</v>
+        <v>1.092266321831309</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.051781069783525</v>
+        <v>1.092266306675108</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.051781039471123</v>
+        <v>1.092266276362707</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.051781024314923</v>
+        <v>1.092266261206506</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.225252353036831</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.051781062205425</v>
+        <v>1.092266299097008</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.051781077361627</v>
+        <v>1.092266314253209</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.225252353036831</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.051781069783525</v>
+        <v>1.092266306675108</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_2_000007.xlsx
+++ b/out/MLP-mamba2_repeat_2_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.3690589350268096</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.474458756368113</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.474458756368113</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.474458756368113</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002844181210889947</v>
+        <v>-0.0001699209252065048</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.278920801865005</v>
+        <v>1.95893731051444</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.562910375102412</v>
+        <v>3.920902784583975</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4916888007696207</v>
+        <v>0.2937513880914304</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.262966305951609</v>
+        <v>2.546839086929872</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6147710428921079</v>
+        <v>0.3672847588940646</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.00089762920324</v>
+        <v>2.987703979971996</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8812712118197029</v>
+        <v>0.5265009600627921</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.149016278064389</v>
+        <v>3.673628628436094</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9427856346348693</v>
+        <v>0.5632520861300723</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.153382412838788</v>
+        <v>4.273670770273044</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9991627454671981</v>
+        <v>0.5969329448351925</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.208994390261886</v>
+        <v>4.904328671704328</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4509035638265819</v>
+        <v>0.2693854016454681</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.11080832819213</v>
+        <v>4.845669004535103</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2177658120858674</v>
+        <v>0.1301001931572877</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.095082773061586</v>
+        <v>4.836274041540564</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1037595390535334</v>
+        <v>0.06198948160568284</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.084661815490806</v>
+        <v>4.830048206657911</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03074286445690105</v>
+        <v>0.01836668780078782</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.04227820877983</v>
+        <v>4.804726797085775</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02033573889862079</v>
+        <v>0.01214805969555254</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.052190043241371</v>
+        <v>4.810647211766772</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01040622909758016</v>
+        <v>0.00621458029730689</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.05265347118358</v>
+        <v>4.810922069395952</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005320242707164701</v>
+        <v>0.003177059016511837</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.052882541436309</v>
+        <v>4.811056922742974</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001996960605948998</v>
+        <v>0.001190878169149118</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.051551935424271</v>
+        <v>4.810259966663066</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001086482907913131</v>
+        <v>0.000646754722034296</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.051726068091265</v>
+        <v>4.810361999950568</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005203164973190552</v>
+        <v>0.0003089183304705398</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.051680323223337</v>
+        <v>4.810332639457483</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003206891438709984</v>
+        <v>0.000189823113252138</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.051800344268736</v>
+        <v>4.81040242546047</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001648459109850995</v>
+        <v>9.690754659105971e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.05181018771423</v>
+        <v>4.810406304246605</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.792472985516974e-05</v>
+        <v>4.395556340847371e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.051800054917489</v>
+        <v>4.810398243728899</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.744500148827117e-05</v>
+        <v>2.697865944406779e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.051818263607652</v>
+        <v>4.810407224399903</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.947783683037037e-05</v>
+        <v>8.987335331640211e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.051808459664555</v>
+        <v>4.810399365618055</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>5.293691574854516e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.051800582617643</v>
+        <v>4.810392584827585</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.051796492805153</v>
+        <v>4.810388164283735</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.051790625362468</v>
+        <v>4.810382585988611</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.051785556007101</v>
+        <v>4.810377539367543</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.051781191033133</v>
+        <v>4.81037785764776</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.051782282279587</v>
+        <v>4.810378948894217</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.051781592672452</v>
+        <v>4.810378259287081</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.474458756368113</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.051781622984855</v>
+        <v>4.810378289599483</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.051781433532344</v>
+        <v>4.810378100146973</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.051781486579047</v>
+        <v>4.810378153193676</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.051781539625749</v>
+        <v>4.810378206240379</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.051781501735247</v>
+        <v>4.810378168349876</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.051781372907541</v>
+        <v>4.81037803952217</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.051781228923634</v>
+        <v>4.810377895538262</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.051781069783525</v>
+        <v>4.810377736398154</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.05178112283023</v>
+        <v>4.810377789444856</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.051781069783525</v>
+        <v>4.810377736398154</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.051781069783525</v>
+        <v>4.810377736398154</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.051780887909116</v>
+        <v>4.810377554523745</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.051781054627325</v>
+        <v>4.810377721241953</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.051781251657935</v>
+        <v>4.810377918272564</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.051781092517826</v>
+        <v>4.810377759132455</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.051781130408328</v>
+        <v>4.810377797022956</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.05178132743894</v>
+        <v>4.810377994053566</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.051781304704638</v>
+        <v>4.810377971319266</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.051781153142629</v>
+        <v>4.810377819757258</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.051781077361627</v>
+        <v>4.810377743976254</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.051781175876931</v>
+        <v>4.81037784249156</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.051781183455031</v>
+        <v>4.81037785006966</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.051781448688544</v>
+        <v>4.810378115303173</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.051781153142629</v>
+        <v>4.810377819757258</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.051781395641843</v>
+        <v>4.81037806225647</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.051781479000946</v>
+        <v>4.810378145615575</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.051781312282737</v>
+        <v>4.810377978897367</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.051781501735247</v>
+        <v>4.810378168349876</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.051781153142629</v>
+        <v>4.810377819757258</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.051780948533919</v>
+        <v>4.810377615148547</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.051781062205425</v>
+        <v>4.810377728820053</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.051781077361627</v>
+        <v>4.810377743976254</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.051780842440515</v>
+        <v>4.810377509055142</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.051780903065316</v>
+        <v>4.810377569679945</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.05178077423761</v>
+        <v>4.810377440852238</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.051780910643417</v>
+        <v>4.810377577258046</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.051781084939726</v>
+        <v>4.810377751554354</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.474458756368113</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.051781228923634</v>
+        <v>4.810377895538262</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.051781062205425</v>
+        <v>4.810377728820053</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.051781054627325</v>
+        <v>4.810377721241953</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.05178076665951</v>
+        <v>4.810377433274137</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.418340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.05178078181571</v>
+        <v>4.810377448430339</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.051781009158724</v>
+        <v>4.810377675773351</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.05178099400252</v>
+        <v>4.810377660617149</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.051781100095928</v>
+        <v>4.810377766710555</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.051780827284311</v>
+        <v>4.810377493898941</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.418340913531692</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.051780925799617</v>
+        <v>4.810377592414246</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.051781077361627</v>
+        <v>4.810377743976254</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.051781092517826</v>
+        <v>4.810377759132455</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.051781069783525</v>
+        <v>4.810377736398154</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.818340913531692</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.051781153142629</v>
+        <v>4.810377819757258</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.051781251657935</v>
+        <v>4.810377918272564</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.051781084939726</v>
+        <v>4.810377751554354</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.051781069783525</v>
+        <v>4.810377736398154</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.051781039471123</v>
+        <v>4.810377706085752</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.051781024314923</v>
+        <v>4.810377690929552</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.051781062205425</v>
+        <v>4.810377728820053</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.051781077361627</v>
+        <v>4.810377743976254</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.051781069783525</v>
+        <v>4.810377736398154</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_2_000007.xlsx
+++ b/out/MLP-mamba2_repeat_2_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3237389028072357</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.3690589350268096</v>
+        <v>-0.4400000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5386665463447571</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.44286248087883</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.1779121160507202</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4809249639511108</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.3866661190986633</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3549427688121796</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.2220446914434433</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4848959147930145</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3145347535610199</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.3344185352325439</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3095456063747406</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5538094639778137</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.2068999260663986</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.1942347437143326</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.474458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.2704601287841797</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.474458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4510980844497681</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.254913330078125</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.3054730892181396</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.02121970456183539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.6817843914031982</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.7599643468856812</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.612576626421732</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.8627323508262634</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3355307281017303</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.455289363861084</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.474458756368113</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4506559073925018</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3599775731563568</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3173389732837677</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.8064872622489929</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3736843466758728</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4824899137020111</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4360262155532837</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.2119968831539154</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.02121970456183539</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.51837158203125</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5714821815490723</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.612576626421732</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.8613226413726807</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.612576626421732</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.9592170119285583</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5508509278297424</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.612576626421732</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.7088344693183899</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001699209252065048</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.95893731051444</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.2550274133682251</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.9168981654917838</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.920902784583975</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2937513880914304</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5591342449188232</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7168981654917838</v>
+        <v>-0.16</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.546839086929872</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3672847588940646</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.6353968977928162</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.16</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.987703979971996</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.5265009600627921</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.9043302536010742</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.612576626421732</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.673628628436094</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.5632520861300723</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9401293992996216</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.612576626421732</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.273670770273044</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5969329448351925</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7890146374702454</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.612576626421732</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.904328671704328</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2693854016454681</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5725247263908386</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>4.845669004535103</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1301001931572877</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.08705643564462662</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>4.836274041540564</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.06198948160568284</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.1129022687673569</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>4.830048206657911</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01836668780078782</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4758622944355011</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>4.804726797085775</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01214805969555254</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4113087058067322</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>4.810647211766772</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00621458029730689</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.1066051125526428</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>4.810922069395952</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003177059016511837</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.2598532140254974</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>4.811056922742974</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001190878169149118</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.436826765537262</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>4.810259966663066</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000646754722034296</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3687923550605774</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>4.810361999950568</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003089183304705398</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.6794524192810059</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
-        <v>4.810332639457483</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000189823113252138</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.5208286643028259</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>4.81040242546047</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>9.690754659105971e-05</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.2049187421798706</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>4.810406304246605</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.395556340847371e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.9656744003295898</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>4.810398243728899</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.697865944406779e-05</v>
+        <v>2.186207393301694e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.3377269506454468</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>4.810407224399903</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>8.987335331640211e-06</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.06103739142417908</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>4.810399365618055</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>1.176214944912711e-06</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3693456947803497</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>4.810392584827585</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.147480696439743</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>4.810388164283735</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.2713076770305634</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>4.810382585988611</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.8931611776351929</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>4.810377539367543</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.9520307779312134</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.612576626421732</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>4.81037785764776</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.8544352650642395</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>4.810378948894217</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.1056360006332397</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>4.810378259287081</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.02630009688436985</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.474458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>4.810378289599483</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.1625361740589142</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>4.810378100146973</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.2995352149009705</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>4.810378153193676</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.1357425600290298</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>4.810378206240379</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.1637602895498276</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>4.810378168349876</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.1617253571748734</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>4.81037803952217</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.1929649710655212</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>4.810377895538262</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3483034372329712</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>4.810377736398154</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.2851764261722565</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>4.810377789444856</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3566364347934723</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>4.810377736398154</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.1229662522673607</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>4.810377736398154</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.8333259224891663</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>4.810377554523745</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.771335780620575</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>4.810377721241953</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.09594723582267761</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>4.810377918272564</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3837158977985382</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>4.810377759132455</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.7163030505180359</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>4.810377797022956</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.562407374382019</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>4.810377994053566</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.143138974905014</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>4.810377971319266</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.2422084510326385</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>4.810377819757258</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.4928636252880096</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>4.810377743976254</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.3676227331161499</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>4.81037784249156</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.7175486087799072</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.02121970456183539</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>4.81037785006966</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.2521606087684631</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>4.810378115303173</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.5867016911506653</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>4.810377819757258</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.6803462505340576</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>4.81037806225647</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.07793587446212769</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>4.810378145615575</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.8767104148864746</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>4.810377978897367</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.1023029312491417</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>4.810378168349876</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.1382360458374023</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>4.810377819757258</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2695964574813843</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>4.810377615148547</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4155240654945374</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>4.810377728820053</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.09925742447376251</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>4.810377743976254</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4529838263988495</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>4.810377509055142</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.1285402029752731</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.02121970456183539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>4.810377569679945</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.6797975897789001</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>4.810377440852238</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.915170431137085</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>4.810377577258046</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.49582639336586</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>4.810377751554354</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.130963608622551</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.474458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC105" t="n">
-        <v>4.810377895538262</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4036431014537811</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>4.810377728820053</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.04608558118343353</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>4.810377721241953</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3734994530677795</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>4.810377433274137</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.8357022404670715</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>4.810377448430339</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3504664599895477</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9168981654917838</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>4.810377675773351</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.7377722263336182</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>4.810377660617149</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.05720209702849388</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>4.810377766710555</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.4782252907752991</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>4.810377493898941</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.739159882068634</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>4.810377592414246</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4258486926555634</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>4.810377743976254</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4572616815567017</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>4.810377759132455</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4766054749488831</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.02121970456183539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>4.810377736398154</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.5307502150535583</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.02121970456183539</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>4.810377819757258</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.2563648223876953</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.2212197045618354</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>4.810377918272564</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.1980475038290024</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>4.810377751554354</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.391763299703598</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>4.810377736398154</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.2978044450283051</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>4.810377706085752</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4825020134449005</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>4.810377690929552</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.409794807434082</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>4.810377728820053</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3770228922367096</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.65</v>
       </c>
       <c r="JC125" t="n">
-        <v>4.810377743976254</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.3309136927127838</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.72</v>
       </c>
       <c r="JC126" t="n">
-        <v>4.810377736398154</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_2_000007.xlsx
+++ b/out/MLP-mamba2_repeat_2_000007.xlsx
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.1779121160507202</v>
+        <v>0.177912101149559</v>
       </c>
       <c r="JB5" t="n">
         <v>0.4399999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.2220446914434433</v>
+        <v>0.2220447212457657</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.4848959147930145</v>
+        <v>0.4848960041999817</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.3145347535610199</v>
+        <v>0.3145348131656647</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.7199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.3344185352325439</v>
+        <v>0.3344185054302216</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.4399999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.5538094639778137</v>
+        <v>0.5538095235824585</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.7199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.2068999260663986</v>
+        <v>0.2068999111652374</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.1942347437143326</v>
+        <v>0.1942347884178162</v>
       </c>
       <c r="JB16" t="n">
         <v>0.16</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.2704601287841797</v>
+        <v>0.2704601585865021</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.1199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.3054730892181396</v>
+        <v>0.3054730594158173</v>
       </c>
       <c r="JB20" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3355307281017303</v>
+        <v>0.3355308175086975</v>
       </c>
       <c r="JB24" t="n">
         <v>0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.455289363861084</v>
+        <v>0.4552894532680511</v>
       </c>
       <c r="JB25" t="n">
         <v>0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.3599775731563568</v>
+        <v>0.3599775433540344</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.4360262155532837</v>
+        <v>0.4360262453556061</v>
       </c>
       <c r="JB32" t="n">
         <v>0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.5714821815490723</v>
+        <v>0.5714821219444275</v>
       </c>
       <c r="JB35" t="n">
         <v>0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.2550274133682251</v>
+        <v>0.2550273835659027</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.1600000000000001</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.08705643564462662</v>
+        <v>0.08705642074346542</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.4399999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.1129022687673569</v>
+        <v>0.1129022985696793</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.1066051125526428</v>
+        <v>0.106605090200901</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.2598532140254974</v>
+        <v>0.2598531544208527</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.436826765537262</v>
+        <v>0.4368268549442291</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.3687923550605774</v>
+        <v>0.368792325258255</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.5799999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.2049187421798706</v>
+        <v>0.2049187123775482</v>
       </c>
       <c r="JB57" t="n">
         <v>0.3</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.3377269506454468</v>
+        <v>0.3377270698547363</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.1199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.06103739142417908</v>
+        <v>0.06103735044598579</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.3693456947803497</v>
+        <v>0.3693456649780273</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.2713076770305634</v>
+        <v>0.271307647228241</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.1056360006332397</v>
+        <v>0.1056360453367233</v>
       </c>
       <c r="JB67" t="n">
         <v>0.16</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.02630009688436985</v>
+        <v>0.02630008384585381</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.1625361740589142</v>
+        <v>0.1625362038612366</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.2995352149009705</v>
+        <v>0.2995351850986481</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.1637602895498276</v>
+        <v>0.1637603342533112</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1617253571748734</v>
+        <v>0.1617253124713898</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.8599999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.1929649710655212</v>
+        <v>0.1929649114608765</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.8599999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.2851764261722565</v>
+        <v>0.2851763963699341</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.1199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.1229662522673607</v>
+        <v>0.1229662224650383</v>
       </c>
       <c r="JB78" t="n">
         <v>0.3</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.09594723582267761</v>
+        <v>0.09594722092151642</v>
       </c>
       <c r="JB81" t="n">
         <v>0.5799999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.562407374382019</v>
+        <v>0.5624074339866638</v>
       </c>
       <c r="JB84" t="n">
         <v>0.16</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.2422084510326385</v>
+        <v>0.2422084361314774</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.4928636252880096</v>
+        <v>0.4928636848926544</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.7175486087799072</v>
+        <v>0.7175485491752625</v>
       </c>
       <c r="JB89" t="n">
         <v>0.5799999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.5867016911506653</v>
+        <v>0.5867016315460205</v>
       </c>
       <c r="JB91" t="n">
         <v>0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.6803462505340576</v>
+        <v>0.6803463101387024</v>
       </c>
       <c r="JB92" t="n">
         <v>0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.07793587446212769</v>
+        <v>0.07793588936328888</v>
       </c>
       <c r="JB93" t="n">
         <v>0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.1382360458374023</v>
+        <v>0.1382360607385635</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.09925742447376251</v>
+        <v>0.09925740957260132</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.1285402029752731</v>
+        <v>0.1285401731729507</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.915170431137085</v>
+        <v>0.9151703715324402</v>
       </c>
       <c r="JB103" t="n">
         <v>0.4399999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.49582639336586</v>
+        <v>0.4958263337612152</v>
       </c>
       <c r="JB104" t="n">
         <v>0.4399999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.130963608622551</v>
+        <v>0.1309635639190674</v>
       </c>
       <c r="JB105" t="n">
         <v>0.16</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.4036431014537811</v>
+        <v>0.4036431610584259</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.7199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.04608558118343353</v>
+        <v>0.04608558863401413</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.8357022404670715</v>
+        <v>0.8357021808624268</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.4399999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.7377722263336182</v>
+        <v>0.7377722859382629</v>
       </c>
       <c r="JB111" t="n">
         <v>0.4399999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.05720209702849388</v>
+        <v>0.05720211192965508</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.4782252907752991</v>
+        <v>0.4782252311706543</v>
       </c>
       <c r="JB113" t="n">
         <v>0.4399999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.739159882068634</v>
+        <v>0.7391599416732788</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.4258486926555634</v>
+        <v>0.4258487522602081</v>
       </c>
       <c r="JB115" t="n">
         <v>0.5799999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.4766054749488831</v>
+        <v>0.4766054153442383</v>
       </c>
       <c r="JB117" t="n">
         <v>0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.391763299703598</v>
+        <v>0.3917632699012756</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.8599999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.409794807434082</v>
+        <v>0.4097947776317596</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.5799999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.3770228922367096</v>
+        <v>0.3770228624343872</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.65</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.3309136927127838</v>
+        <v>0.3309136629104614</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.72</v>
